--- a/document/BigData Project_开发日报 .xlsx
+++ b/document/BigData Project_开发日报 .xlsx
@@ -1409,7 +1409,7 @@
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>基于Spark+AI的冷启动音乐与视频混合推荐系统</t>
+          <t>基于 Spark 大数据的用户行为实时分析与混合推荐系统</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
